--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N122_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N122_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.98623279792027</v>
+        <v>10.72276282966204</v>
       </c>
       <c r="D2" t="n">
-        <v>48.66809233071614</v>
+        <v>7.908565003741374</v>
       </c>
       <c r="E2" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F2" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.91773262303123</v>
+        <v>7.949131551242576</v>
       </c>
       <c r="D3" t="n">
-        <v>38.33079701754191</v>
+        <v>6.228754515350561</v>
       </c>
       <c r="E3" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F3" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.58412843946115</v>
+        <v>8.382420871412437</v>
       </c>
       <c r="D4" t="n">
-        <v>10.95313374454548</v>
+        <v>1.779884233488641</v>
       </c>
       <c r="E4" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F4" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.95944101977754</v>
+        <v>3.40590916571385</v>
       </c>
       <c r="D5" t="n">
-        <v>20.87421090538735</v>
+        <v>3.392059272125445</v>
       </c>
       <c r="E5" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F5" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.6074075062636</v>
+        <v>7.248703719767835</v>
       </c>
       <c r="D6" t="n">
-        <v>40.40589121220044</v>
+        <v>6.565957321982571</v>
       </c>
       <c r="E6" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F6" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.58858000300676</v>
+        <v>3.8331442504886</v>
       </c>
       <c r="D7" t="n">
-        <v>21.11274314598588</v>
+        <v>3.430820761222705</v>
       </c>
       <c r="E7" t="n">
-        <v>15.81835140096466</v>
+        <v>2.570482102656757</v>
       </c>
       <c r="F7" t="n">
-        <v>13.23637082004008</v>
+        <v>2.150910258256513</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
